--- a/docs/OSC_Memgine_Product_Import.xlsx
+++ b/docs/OSC_Memgine_Product_Import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFC3FE6-EB6F-4375-89F6-CE52317C9DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9820BACB-4C1C-40E5-906E-154E7EDE859C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
